--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/8426-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/8426-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DD6D865-C675-4BC1-9000-3BB3EFDACE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ACD0C0CC-C055-4C36-B36D-5AE3EFCC556A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{7D2C0B73-72CA-4E2B-B08F-B63279D9A0E5}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{99005FEA-8526-4C58-8A1F-2006299D090A}"/>
   </bookViews>
   <sheets>
     <sheet name="8426-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1475,27 +1475,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6F03121-8844-4850-9304-6E4DB8E2671F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA53AD6-D91E-4237-92DC-A30E5EDF1BD1}">
   <dimension ref="A1:X34"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.875" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1529,7 +1529,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1565,7 +1565,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1685,7 +1685,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1905,7 +1905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2024</v>
       </c>
@@ -1977,7 +1977,7 @@
         <v>9.8800000000000008</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>9.8800000000000008</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2199,7 +2199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>2023</v>
       </c>
@@ -2271,7 +2271,7 @@
         <v>6.61</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2345,7 +2345,7 @@
         <v>6.61</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2419,7 +2419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="39">
         <v>2022</v>
       </c>
@@ -2491,7 +2491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>29</v>
       </c>
@@ -2565,7 +2565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>29</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2021</v>
       </c>
@@ -2711,7 +2711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2859,7 +2859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="39">
         <v>2020</v>
       </c>
@@ -2931,7 +2931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>29</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>29</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>2019</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="39">
         <v>2018</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2017</v>
       </c>
@@ -3295,7 +3295,7 @@
         <v>8.7899999999999991</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="39">
         <v>2016</v>
       </c>
@@ -3367,7 +3367,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2015</v>
       </c>
@@ -3439,7 +3439,7 @@
         <v>9.73</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <v>2014</v>
       </c>
@@ -3511,7 +3511,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>2013</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>8.02</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="39">
         <v>2012</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>7.23</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>2011</v>
       </c>
@@ -3727,7 +3727,7 @@
         <v>9.56</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="39">
         <v>2010</v>
       </c>
@@ -3799,7 +3799,7 @@
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37" t="s">
         <v>44</v>
       </c>
